--- a/artfynd/A 22161-2024 artfynd.xlsx
+++ b/artfynd/A 22161-2024 artfynd.xlsx
@@ -3523,10 +3523,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118328996</v>
+        <v>118329027</v>
       </c>
       <c r="B27" t="n">
-        <v>78484</v>
+        <v>77421</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3539,21 +3539,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537387</v>
+        <v>537517</v>
       </c>
       <c r="R27" t="n">
-        <v>7199785</v>
+        <v>7199772</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,7 +3635,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118329023</v>
+        <v>118328996</v>
       </c>
       <c r="B28" t="n">
         <v>78484</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537496</v>
+        <v>537387</v>
       </c>
       <c r="R28" t="n">
-        <v>7199805</v>
+        <v>7199785</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3747,10 +3747,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118329010</v>
+        <v>118329023</v>
       </c>
       <c r="B29" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3763,21 +3763,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537411</v>
+        <v>537496</v>
       </c>
       <c r="R29" t="n">
-        <v>7200013</v>
+        <v>7199805</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118329027</v>
+        <v>118329010</v>
       </c>
       <c r="B30" t="n">
-        <v>77421</v>
+        <v>90522</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,21 +3875,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537517</v>
+        <v>537411</v>
       </c>
       <c r="R30" t="n">
-        <v>7199772</v>
+        <v>7200013</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5325,10 +5325,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118329041</v>
+        <v>118329029</v>
       </c>
       <c r="B43" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,39 +5341,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>537669</v>
+        <v>537488</v>
       </c>
       <c r="R43" t="n">
-        <v>7199580</v>
+        <v>7199796</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5405,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5415,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5442,10 +5437,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118329029</v>
+        <v>118329041</v>
       </c>
       <c r="B44" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5458,34 +5453,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>537488</v>
+        <v>537669</v>
       </c>
       <c r="R44" t="n">
-        <v>7199796</v>
+        <v>7199580</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5517,7 +5517,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD44" t="b">

--- a/artfynd/A 22161-2024 artfynd.xlsx
+++ b/artfynd/A 22161-2024 artfynd.xlsx
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118329014</v>
+        <v>118329015</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>90518</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,21 +1826,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537395</v>
+        <v>537389</v>
       </c>
       <c r="R12" t="n">
-        <v>7200052</v>
+        <v>7200072</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118329015</v>
+        <v>118329014</v>
       </c>
       <c r="B13" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1938,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1962,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537389</v>
+        <v>537395</v>
       </c>
       <c r="R13" t="n">
-        <v>7200072</v>
+        <v>7200052</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -3523,10 +3523,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118329027</v>
+        <v>118328996</v>
       </c>
       <c r="B27" t="n">
-        <v>77421</v>
+        <v>78484</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3539,21 +3539,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3563,10 +3563,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537517</v>
+        <v>537387</v>
       </c>
       <c r="R27" t="n">
-        <v>7199772</v>
+        <v>7199785</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,7 +3635,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118328996</v>
+        <v>118329023</v>
       </c>
       <c r="B28" t="n">
         <v>78484</v>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537387</v>
+        <v>537496</v>
       </c>
       <c r="R28" t="n">
-        <v>7199785</v>
+        <v>7199805</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3710,7 +3710,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3747,10 +3747,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118329023</v>
+        <v>118329010</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3763,21 +3763,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3787,10 +3787,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537496</v>
+        <v>537411</v>
       </c>
       <c r="R29" t="n">
-        <v>7199805</v>
+        <v>7200013</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118329010</v>
+        <v>118329027</v>
       </c>
       <c r="B30" t="n">
-        <v>90522</v>
+        <v>77421</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,21 +3875,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537411</v>
+        <v>537517</v>
       </c>
       <c r="R30" t="n">
-        <v>7200013</v>
+        <v>7199772</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118328992</v>
+        <v>118329032</v>
       </c>
       <c r="B31" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537379</v>
+        <v>537478</v>
       </c>
       <c r="R31" t="n">
-        <v>7199772</v>
+        <v>7199763</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4083,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118329032</v>
+        <v>118328992</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
+        <v>90518</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4099,21 +4099,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537478</v>
+        <v>537379</v>
       </c>
       <c r="R32" t="n">
-        <v>7199763</v>
+        <v>7199772</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 22161-2024 artfynd.xlsx
+++ b/artfynd/A 22161-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118329022</v>
+        <v>118328997</v>
       </c>
       <c r="B2" t="n">
         <v>90522</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537492</v>
+        <v>537389</v>
       </c>
       <c r="R2" t="n">
-        <v>7199822</v>
+        <v>7199825</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118329046</v>
+        <v>118329009</v>
       </c>
       <c r="B3" t="n">
         <v>78484</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537684</v>
+        <v>537409</v>
       </c>
       <c r="R3" t="n">
-        <v>7199558</v>
+        <v>7199992</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118329026</v>
+        <v>118329029</v>
       </c>
       <c r="B4" t="n">
         <v>78484</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537517</v>
+        <v>537488</v>
       </c>
       <c r="R4" t="n">
-        <v>7199772</v>
+        <v>7199796</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118329025</v>
+        <v>118329026</v>
       </c>
       <c r="B5" t="n">
         <v>78484</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537489</v>
+        <v>537517</v>
       </c>
       <c r="R5" t="n">
-        <v>7199777</v>
+        <v>7199772</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118329007</v>
+        <v>118328995</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537391</v>
+        <v>537374</v>
       </c>
       <c r="R6" t="n">
-        <v>7200021</v>
+        <v>7199782</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118329036</v>
+        <v>118329007</v>
       </c>
       <c r="B7" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,39 +1251,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537378</v>
+        <v>537391</v>
       </c>
       <c r="R7" t="n">
-        <v>7199728</v>
+        <v>7200021</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118329038</v>
+        <v>118329005</v>
       </c>
       <c r="B8" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,39 +1363,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537273</v>
+        <v>537438</v>
       </c>
       <c r="R8" t="n">
-        <v>7199736</v>
+        <v>7199979</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1459,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118329001</v>
+        <v>118329037</v>
       </c>
       <c r="B9" t="n">
         <v>78484</v>
@@ -1509,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537409</v>
+        <v>537378</v>
       </c>
       <c r="R9" t="n">
-        <v>7199912</v>
+        <v>7199728</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118329039</v>
+        <v>118329027</v>
       </c>
       <c r="B10" t="n">
-        <v>57290</v>
+        <v>77421</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,39 +1587,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537668</v>
+        <v>537517</v>
       </c>
       <c r="R10" t="n">
-        <v>7199586</v>
+        <v>7199772</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118329002</v>
+        <v>118329008</v>
       </c>
       <c r="B11" t="n">
-        <v>77421</v>
+        <v>57290</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,34 +1699,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537439</v>
+        <v>537409</v>
       </c>
       <c r="R11" t="n">
-        <v>7199979</v>
+        <v>7199992</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118329015</v>
+        <v>118329020</v>
       </c>
       <c r="B12" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537389</v>
+        <v>537526</v>
       </c>
       <c r="R12" t="n">
-        <v>7200072</v>
+        <v>7199903</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118329014</v>
+        <v>118329003</v>
       </c>
       <c r="B13" t="n">
-        <v>78484</v>
+        <v>74596</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,21 +1928,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1962,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537395</v>
+        <v>537439</v>
       </c>
       <c r="R13" t="n">
-        <v>7200052</v>
+        <v>7199979</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118328994</v>
+        <v>118329013</v>
       </c>
       <c r="B14" t="n">
-        <v>90469</v>
+        <v>56494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,38 +2036,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537379</v>
+        <v>537394</v>
       </c>
       <c r="R14" t="n">
-        <v>7199772</v>
+        <v>7200053</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118328995</v>
+        <v>118329006</v>
       </c>
       <c r="B15" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,34 +2166,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537374</v>
+        <v>537391</v>
       </c>
       <c r="R15" t="n">
-        <v>7199782</v>
+        <v>7200021</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118329030</v>
+        <v>118329001</v>
       </c>
       <c r="B16" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,21 +2292,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537477</v>
+        <v>537409</v>
       </c>
       <c r="R16" t="n">
-        <v>7199754</v>
+        <v>7199912</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118329020</v>
+        <v>118329015</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>90518</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,21 +2404,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2410,10 +2428,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537526</v>
+        <v>537389</v>
       </c>
       <c r="R17" t="n">
-        <v>7199903</v>
+        <v>7200072</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,7 +2500,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118329042</v>
+        <v>118328993</v>
       </c>
       <c r="B18" t="n">
         <v>78484</v>
@@ -2522,10 +2540,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537669</v>
+        <v>537379</v>
       </c>
       <c r="R18" t="n">
-        <v>7199580</v>
+        <v>7199772</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2557,7 +2575,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2567,7 +2585,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,10 +2612,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118329000</v>
+        <v>118329018</v>
       </c>
       <c r="B19" t="n">
-        <v>90500</v>
+        <v>78484</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2610,21 +2628,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2634,10 +2652,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537409</v>
+        <v>537514</v>
       </c>
       <c r="R19" t="n">
-        <v>7199912</v>
+        <v>7200002</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2669,7 +2687,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2679,7 +2697,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,7 +2724,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118329009</v>
+        <v>118329040</v>
       </c>
       <c r="B20" t="n">
         <v>78484</v>
@@ -2746,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537409</v>
+        <v>537668</v>
       </c>
       <c r="R20" t="n">
-        <v>7199992</v>
+        <v>7199583</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2781,7 +2799,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2791,7 +2809,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,10 +2836,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118329043</v>
+        <v>118328999</v>
       </c>
       <c r="B21" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,39 +2852,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537669</v>
+        <v>537388</v>
       </c>
       <c r="R21" t="n">
-        <v>7199575</v>
+        <v>7199825</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2898,7 +2911,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,7 +2921,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2935,10 +2948,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118329013</v>
+        <v>118328994</v>
       </c>
       <c r="B22" t="n">
-        <v>56494</v>
+        <v>90469</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2947,52 +2960,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537394</v>
+        <v>537379</v>
       </c>
       <c r="R22" t="n">
-        <v>7200053</v>
+        <v>7199772</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3024,7 +3023,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3034,7 +3033,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,10 +3060,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118328999</v>
+        <v>118329030</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>90518</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3077,21 +3076,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3101,10 +3100,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537388</v>
+        <v>537477</v>
       </c>
       <c r="R23" t="n">
-        <v>7199825</v>
+        <v>7199754</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3136,7 +3135,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3146,7 +3145,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3173,7 +3172,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118328993</v>
+        <v>118329025</v>
       </c>
       <c r="B24" t="n">
         <v>78484</v>
@@ -3213,10 +3212,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537379</v>
+        <v>537489</v>
       </c>
       <c r="R24" t="n">
-        <v>7199772</v>
+        <v>7199777</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3248,7 +3247,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3258,7 +3257,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3285,10 +3284,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118329012</v>
+        <v>118329017</v>
       </c>
       <c r="B25" t="n">
-        <v>56494</v>
+        <v>74588</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3301,48 +3300,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537396</v>
+        <v>537512</v>
       </c>
       <c r="R25" t="n">
-        <v>7200050</v>
+        <v>7200008</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3374,7 +3359,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3384,7 +3369,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3411,10 +3396,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118328997</v>
+        <v>118329031</v>
       </c>
       <c r="B26" t="n">
-        <v>90522</v>
+        <v>96801</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3423,25 +3408,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3451,10 +3436,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537389</v>
+        <v>537476</v>
       </c>
       <c r="R26" t="n">
-        <v>7199825</v>
+        <v>7199761</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3486,7 +3471,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3496,7 +3481,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3523,10 +3508,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118328996</v>
+        <v>118329038</v>
       </c>
       <c r="B27" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3539,34 +3524,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537387</v>
+        <v>537273</v>
       </c>
       <c r="R27" t="n">
-        <v>7199785</v>
+        <v>7199736</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3598,7 +3588,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3608,7 +3598,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,10 +3625,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118329023</v>
+        <v>118329043</v>
       </c>
       <c r="B28" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3651,34 +3641,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537496</v>
+        <v>537669</v>
       </c>
       <c r="R28" t="n">
-        <v>7199805</v>
+        <v>7199575</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3710,7 +3705,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3720,7 +3715,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3747,10 +3742,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118329010</v>
+        <v>118329044</v>
       </c>
       <c r="B29" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3763,21 +3758,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3787,10 +3782,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537411</v>
+        <v>537667</v>
       </c>
       <c r="R29" t="n">
-        <v>7200013</v>
+        <v>7199573</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3822,7 +3817,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,7 +3827,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3854,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118329027</v>
+        <v>118329046</v>
       </c>
       <c r="B30" t="n">
-        <v>77421</v>
+        <v>78484</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,21 +3870,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,10 +3894,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537517</v>
+        <v>537684</v>
       </c>
       <c r="R30" t="n">
-        <v>7199772</v>
+        <v>7199558</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3934,7 +3929,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3939,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3966,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118329032</v>
+        <v>118329036</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,34 +3982,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537478</v>
+        <v>537378</v>
       </c>
       <c r="R31" t="n">
-        <v>7199763</v>
+        <v>7199728</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4083,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118328992</v>
+        <v>118329045</v>
       </c>
       <c r="B32" t="n">
-        <v>90518</v>
+        <v>57290</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4099,34 +4099,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537379</v>
+        <v>537683</v>
       </c>
       <c r="R32" t="n">
-        <v>7199772</v>
+        <v>7199559</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4158,7 +4163,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4168,7 +4173,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4195,10 +4200,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118329045</v>
+        <v>118329002</v>
       </c>
       <c r="B33" t="n">
-        <v>57290</v>
+        <v>77421</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4211,39 +4216,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537683</v>
+        <v>537439</v>
       </c>
       <c r="R33" t="n">
-        <v>7199559</v>
+        <v>7199979</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4312,7 +4312,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118329037</v>
+        <v>118329011</v>
       </c>
       <c r="B34" t="n">
         <v>78484</v>
@@ -4352,10 +4352,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537378</v>
+        <v>537396</v>
       </c>
       <c r="R34" t="n">
-        <v>7199728</v>
+        <v>7200015</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4387,7 +4387,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4424,10 +4424,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118329034</v>
+        <v>118329016</v>
       </c>
       <c r="B35" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4440,39 +4440,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537458</v>
+        <v>537389</v>
       </c>
       <c r="R35" t="n">
-        <v>7199716</v>
+        <v>7200072</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4504,7 +4499,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4514,7 +4509,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4541,10 +4536,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118329028</v>
+        <v>118329041</v>
       </c>
       <c r="B36" t="n">
-        <v>74596</v>
+        <v>57290</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4557,34 +4552,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537517</v>
+        <v>537669</v>
       </c>
       <c r="R36" t="n">
-        <v>7199772</v>
+        <v>7199580</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4653,10 +4653,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118329003</v>
+        <v>118329019</v>
       </c>
       <c r="B37" t="n">
-        <v>74596</v>
+        <v>78566</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4669,21 +4669,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6440</v>
+        <v>864</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4693,10 +4693,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537439</v>
+        <v>537526</v>
       </c>
       <c r="R37" t="n">
-        <v>7199979</v>
+        <v>7199903</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4765,7 +4765,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118329044</v>
+        <v>118329014</v>
       </c>
       <c r="B38" t="n">
         <v>78484</v>
@@ -4805,10 +4805,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537667</v>
+        <v>537395</v>
       </c>
       <c r="R38" t="n">
-        <v>7199573</v>
+        <v>7200052</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4877,7 +4877,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118329016</v>
+        <v>118329032</v>
       </c>
       <c r="B39" t="n">
         <v>78484</v>
@@ -4917,10 +4917,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537389</v>
+        <v>537478</v>
       </c>
       <c r="R39" t="n">
-        <v>7200072</v>
+        <v>7199763</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4989,10 +4989,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118329031</v>
+        <v>118329000</v>
       </c>
       <c r="B40" t="n">
-        <v>96801</v>
+        <v>90500</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5001,25 +5001,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5029,10 +5029,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537476</v>
+        <v>537409</v>
       </c>
       <c r="R40" t="n">
-        <v>7199761</v>
+        <v>7199912</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5064,7 +5064,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5101,10 +5101,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118329005</v>
+        <v>118328992</v>
       </c>
       <c r="B41" t="n">
-        <v>78484</v>
+        <v>90518</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5117,21 +5117,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5141,10 +5141,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537438</v>
+        <v>537379</v>
       </c>
       <c r="R41" t="n">
-        <v>7199979</v>
+        <v>7199772</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5325,7 +5325,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118329029</v>
+        <v>118329023</v>
       </c>
       <c r="B43" t="n">
         <v>78484</v>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>537488</v>
+        <v>537496</v>
       </c>
       <c r="R43" t="n">
-        <v>7199796</v>
+        <v>7199805</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5437,10 +5437,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118329041</v>
+        <v>118329010</v>
       </c>
       <c r="B44" t="n">
-        <v>57290</v>
+        <v>90522</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5453,39 +5453,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>537669</v>
+        <v>537411</v>
       </c>
       <c r="R44" t="n">
-        <v>7199580</v>
+        <v>7200013</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5517,7 +5512,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5527,7 +5522,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5554,10 +5549,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118329011</v>
+        <v>118329012</v>
       </c>
       <c r="B45" t="n">
-        <v>78484</v>
+        <v>56494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5570,24 +5565,38 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
@@ -5597,7 +5606,7 @@
         <v>537396</v>
       </c>
       <c r="R45" t="n">
-        <v>7200015</v>
+        <v>7200050</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5629,7 +5638,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5639,7 +5648,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5666,7 +5675,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118329008</v>
+        <v>118329039</v>
       </c>
       <c r="B46" t="n">
         <v>57290</v>
@@ -5711,10 +5720,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>537409</v>
+        <v>537668</v>
       </c>
       <c r="R46" t="n">
-        <v>7199992</v>
+        <v>7199586</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5746,7 +5755,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5756,7 +5765,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5783,10 +5792,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118329017</v>
+        <v>118329028</v>
       </c>
       <c r="B47" t="n">
-        <v>74588</v>
+        <v>74596</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5799,21 +5808,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5823,10 +5832,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>537512</v>
+        <v>537517</v>
       </c>
       <c r="R47" t="n">
-        <v>7200008</v>
+        <v>7199772</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5858,7 +5867,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5868,7 +5877,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5895,7 +5904,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118329018</v>
+        <v>118329042</v>
       </c>
       <c r="B48" t="n">
         <v>78484</v>
@@ -5935,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>537514</v>
+        <v>537669</v>
       </c>
       <c r="R48" t="n">
-        <v>7200002</v>
+        <v>7199580</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5970,7 +5979,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5980,7 +5989,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6007,10 +6016,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118329006</v>
+        <v>118328996</v>
       </c>
       <c r="B49" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6023,48 +6032,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>537391</v>
+        <v>537387</v>
       </c>
       <c r="R49" t="n">
-        <v>7200021</v>
+        <v>7199785</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6096,7 +6091,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6106,7 +6101,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6133,10 +6128,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118329019</v>
+        <v>118329022</v>
       </c>
       <c r="B50" t="n">
-        <v>78566</v>
+        <v>90522</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6149,21 +6144,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>864</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6173,10 +6168,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>537526</v>
+        <v>537492</v>
       </c>
       <c r="R50" t="n">
-        <v>7199903</v>
+        <v>7199822</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6208,7 +6203,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6218,7 +6213,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6245,10 +6240,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118329040</v>
+        <v>118329034</v>
       </c>
       <c r="B51" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6261,34 +6256,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>537668</v>
+        <v>537458</v>
       </c>
       <c r="R51" t="n">
-        <v>7199583</v>
+        <v>7199716</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22161-2024 artfynd.xlsx
+++ b/artfynd/A 22161-2024 artfynd.xlsx
@@ -5325,10 +5325,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118329023</v>
+        <v>118329012</v>
       </c>
       <c r="B43" t="n">
-        <v>78484</v>
+        <v>56494</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,34 +5341,48 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>537496</v>
+        <v>537396</v>
       </c>
       <c r="R43" t="n">
-        <v>7199805</v>
+        <v>7200050</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5400,7 +5414,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5424,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5549,10 +5563,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118329012</v>
+        <v>118329023</v>
       </c>
       <c r="B45" t="n">
-        <v>56494</v>
+        <v>78484</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5565,48 +5579,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>537396</v>
+        <v>537496</v>
       </c>
       <c r="R45" t="n">
-        <v>7200050</v>
+        <v>7199805</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5638,7 +5638,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 22161-2024 artfynd.xlsx
+++ b/artfynd/A 22161-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118328997</v>
+        <v>118329018</v>
       </c>
       <c r="B2" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537389</v>
+        <v>537514</v>
       </c>
       <c r="R2" t="n">
-        <v>7199825</v>
+        <v>7200002</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118329009</v>
+        <v>118329028</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>74596</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537409</v>
+        <v>537517</v>
       </c>
       <c r="R3" t="n">
-        <v>7199992</v>
+        <v>7199772</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118329029</v>
+        <v>118329038</v>
       </c>
       <c r="B4" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537488</v>
+        <v>537273</v>
       </c>
       <c r="R4" t="n">
-        <v>7199796</v>
+        <v>7199736</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118329026</v>
+        <v>118329012</v>
       </c>
       <c r="B5" t="n">
-        <v>78484</v>
+        <v>56494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1032,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537517</v>
+        <v>537396</v>
       </c>
       <c r="R5" t="n">
-        <v>7199772</v>
+        <v>7200050</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118328995</v>
+        <v>118328999</v>
       </c>
       <c r="B6" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537374</v>
+        <v>537388</v>
       </c>
       <c r="R6" t="n">
-        <v>7199782</v>
+        <v>7199825</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1254,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118329007</v>
+        <v>118329016</v>
       </c>
       <c r="B7" t="n">
         <v>78484</v>
@@ -1275,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537391</v>
+        <v>537389</v>
       </c>
       <c r="R7" t="n">
-        <v>7200021</v>
+        <v>7200072</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1366,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118329005</v>
+        <v>118329002</v>
       </c>
       <c r="B8" t="n">
-        <v>78484</v>
+        <v>77421</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1363,21 +1382,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,7 +1406,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537438</v>
+        <v>537439</v>
       </c>
       <c r="R8" t="n">
         <v>7199979</v>
@@ -1459,7 +1478,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118329037</v>
+        <v>118329023</v>
       </c>
       <c r="B9" t="n">
         <v>78484</v>
@@ -1499,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537378</v>
+        <v>537496</v>
       </c>
       <c r="R9" t="n">
-        <v>7199728</v>
+        <v>7199805</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118329027</v>
+        <v>118329014</v>
       </c>
       <c r="B10" t="n">
-        <v>77421</v>
+        <v>78484</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1630,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537517</v>
+        <v>537395</v>
       </c>
       <c r="R10" t="n">
-        <v>7199772</v>
+        <v>7200052</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118329008</v>
+        <v>118329026</v>
       </c>
       <c r="B11" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,39 +1718,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537409</v>
+        <v>537517</v>
       </c>
       <c r="R11" t="n">
-        <v>7199992</v>
+        <v>7199772</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,7 +1814,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118329020</v>
+        <v>118329042</v>
       </c>
       <c r="B12" t="n">
         <v>78484</v>
@@ -1840,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537526</v>
+        <v>537669</v>
       </c>
       <c r="R12" t="n">
-        <v>7199903</v>
+        <v>7199580</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118329003</v>
+        <v>118329022</v>
       </c>
       <c r="B13" t="n">
-        <v>74596</v>
+        <v>90522</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537439</v>
+        <v>537492</v>
       </c>
       <c r="R13" t="n">
-        <v>7199979</v>
+        <v>7199822</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118329013</v>
+        <v>118329030</v>
       </c>
       <c r="B14" t="n">
-        <v>56494</v>
+        <v>90518</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,48 +2054,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>pulli</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537394</v>
+        <v>537477</v>
       </c>
       <c r="R14" t="n">
-        <v>7200053</v>
+        <v>7199754</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,7 +2150,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118329006</v>
+        <v>118329041</v>
       </c>
       <c r="B15" t="n">
         <v>57290</v>
@@ -2183,19 +2183,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2204,10 +2195,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537391</v>
+        <v>537669</v>
       </c>
       <c r="R15" t="n">
-        <v>7200021</v>
+        <v>7199580</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2239,7 +2230,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2249,7 +2240,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2276,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118329001</v>
+        <v>118329013</v>
       </c>
       <c r="B16" t="n">
-        <v>78484</v>
+        <v>56494</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2292,34 +2283,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>pulli</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>537409</v>
+        <v>537394</v>
       </c>
       <c r="R16" t="n">
-        <v>7199912</v>
+        <v>7200053</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2356,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2366,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118329015</v>
+        <v>118329020</v>
       </c>
       <c r="B17" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,21 +2409,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2433,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537389</v>
+        <v>537526</v>
       </c>
       <c r="R17" t="n">
-        <v>7200072</v>
+        <v>7199903</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118328993</v>
+        <v>118328994</v>
       </c>
       <c r="B18" t="n">
-        <v>78484</v>
+        <v>90469</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,25 +2517,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2575,7 +2580,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2585,7 +2590,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2612,10 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118329018</v>
+        <v>118329015</v>
       </c>
       <c r="B19" t="n">
-        <v>78484</v>
+        <v>90518</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2628,21 +2633,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2652,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537514</v>
+        <v>537389</v>
       </c>
       <c r="R19" t="n">
-        <v>7200002</v>
+        <v>7200072</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2687,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2697,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2724,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118329040</v>
+        <v>118329031</v>
       </c>
       <c r="B20" t="n">
-        <v>78484</v>
+        <v>96801</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2741,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2769,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537668</v>
+        <v>537476</v>
       </c>
       <c r="R20" t="n">
-        <v>7199583</v>
+        <v>7199761</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2799,7 +2804,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2809,7 +2814,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2836,7 +2841,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118328999</v>
+        <v>118329025</v>
       </c>
       <c r="B21" t="n">
         <v>78484</v>
@@ -2876,10 +2881,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537388</v>
+        <v>537489</v>
       </c>
       <c r="R21" t="n">
-        <v>7199825</v>
+        <v>7199777</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2911,7 +2916,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2921,7 +2926,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2948,10 +2953,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118328994</v>
+        <v>118329006</v>
       </c>
       <c r="B22" t="n">
-        <v>90469</v>
+        <v>57290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2960,38 +2965,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537379</v>
+        <v>537391</v>
       </c>
       <c r="R22" t="n">
-        <v>7199772</v>
+        <v>7200021</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3023,7 +3042,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3052,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3079,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118329030</v>
+        <v>118329046</v>
       </c>
       <c r="B23" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3076,21 +3095,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3119,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537477</v>
+        <v>537684</v>
       </c>
       <c r="R23" t="n">
-        <v>7199754</v>
+        <v>7199558</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3135,7 +3154,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3164,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,7 +3191,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118329025</v>
+        <v>118329040</v>
       </c>
       <c r="B24" t="n">
         <v>78484</v>
@@ -3212,10 +3231,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537489</v>
+        <v>537668</v>
       </c>
       <c r="R24" t="n">
-        <v>7199777</v>
+        <v>7199583</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3247,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,10 +3303,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118329017</v>
+        <v>118329032</v>
       </c>
       <c r="B25" t="n">
-        <v>74588</v>
+        <v>78484</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3300,21 +3319,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3324,10 +3343,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537512</v>
+        <v>537478</v>
       </c>
       <c r="R25" t="n">
-        <v>7200008</v>
+        <v>7199763</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3359,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3369,7 +3388,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3396,10 +3415,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118329031</v>
+        <v>118329000</v>
       </c>
       <c r="B26" t="n">
-        <v>96801</v>
+        <v>90500</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3408,25 +3427,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>1108</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3436,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537476</v>
+        <v>537409</v>
       </c>
       <c r="R26" t="n">
-        <v>7199761</v>
+        <v>7199912</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3471,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3481,7 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3508,7 +3527,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118329038</v>
+        <v>118329045</v>
       </c>
       <c r="B27" t="n">
         <v>57290</v>
@@ -3553,10 +3572,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537273</v>
+        <v>537683</v>
       </c>
       <c r="R27" t="n">
-        <v>7199736</v>
+        <v>7199559</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3588,7 +3607,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3598,7 +3617,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3742,10 +3761,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118329044</v>
+        <v>118329024</v>
       </c>
       <c r="B29" t="n">
-        <v>78484</v>
+        <v>90522</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3758,21 +3777,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3782,10 +3801,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537667</v>
+        <v>537525</v>
       </c>
       <c r="R29" t="n">
-        <v>7199573</v>
+        <v>7199795</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3817,7 +3836,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3827,7 +3846,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3854,7 +3873,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118329046</v>
+        <v>118329044</v>
       </c>
       <c r="B30" t="n">
         <v>78484</v>
@@ -3894,10 +3913,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537684</v>
+        <v>537667</v>
       </c>
       <c r="R30" t="n">
-        <v>7199558</v>
+        <v>7199573</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3929,7 +3948,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3939,7 +3958,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3966,10 +3985,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118329036</v>
+        <v>118329011</v>
       </c>
       <c r="B31" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3982,39 +4001,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537378</v>
+        <v>537396</v>
       </c>
       <c r="R31" t="n">
-        <v>7199728</v>
+        <v>7200015</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4046,7 +4060,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4070,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4083,10 +4097,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118329045</v>
+        <v>118329029</v>
       </c>
       <c r="B32" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4099,39 +4113,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537683</v>
+        <v>537488</v>
       </c>
       <c r="R32" t="n">
-        <v>7199559</v>
+        <v>7199796</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4163,7 +4172,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4173,7 +4182,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4200,10 +4209,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118329002</v>
+        <v>118329009</v>
       </c>
       <c r="B33" t="n">
-        <v>77421</v>
+        <v>78484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4216,21 +4225,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4240,10 +4249,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537439</v>
+        <v>537409</v>
       </c>
       <c r="R33" t="n">
-        <v>7199979</v>
+        <v>7199992</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4275,7 +4284,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4285,7 +4294,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4312,10 +4321,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118329011</v>
+        <v>118329017</v>
       </c>
       <c r="B34" t="n">
-        <v>78484</v>
+        <v>74588</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4328,21 +4337,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4352,10 +4361,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537396</v>
+        <v>537512</v>
       </c>
       <c r="R34" t="n">
-        <v>7200015</v>
+        <v>7200008</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4387,7 +4396,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4397,7 +4406,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4424,10 +4433,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118329016</v>
+        <v>118329036</v>
       </c>
       <c r="B35" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4440,34 +4449,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537389</v>
+        <v>537378</v>
       </c>
       <c r="R35" t="n">
-        <v>7200072</v>
+        <v>7199728</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4499,7 +4513,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4509,7 +4523,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4536,10 +4550,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118329041</v>
+        <v>118328997</v>
       </c>
       <c r="B36" t="n">
-        <v>57290</v>
+        <v>90522</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4552,39 +4566,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537669</v>
+        <v>537389</v>
       </c>
       <c r="R36" t="n">
-        <v>7199580</v>
+        <v>7199825</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4616,7 +4625,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4626,7 +4635,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4653,10 +4662,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118329019</v>
+        <v>118329008</v>
       </c>
       <c r="B37" t="n">
-        <v>78566</v>
+        <v>57290</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4669,34 +4678,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537526</v>
+        <v>537409</v>
       </c>
       <c r="R37" t="n">
-        <v>7199903</v>
+        <v>7199992</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4728,7 +4742,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4738,7 +4752,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4765,10 +4779,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118329014</v>
+        <v>118329027</v>
       </c>
       <c r="B38" t="n">
-        <v>78484</v>
+        <v>77421</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4781,21 +4795,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4805,10 +4819,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537395</v>
+        <v>537517</v>
       </c>
       <c r="R38" t="n">
-        <v>7200052</v>
+        <v>7199772</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4840,7 +4854,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4850,7 +4864,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4877,10 +4891,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118329032</v>
+        <v>118329019</v>
       </c>
       <c r="B39" t="n">
-        <v>78484</v>
+        <v>78566</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4893,21 +4907,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>864</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4917,10 +4931,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537478</v>
+        <v>537526</v>
       </c>
       <c r="R39" t="n">
-        <v>7199763</v>
+        <v>7199903</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4952,7 +4966,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4962,7 +4976,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4989,10 +5003,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118329000</v>
+        <v>118328996</v>
       </c>
       <c r="B40" t="n">
-        <v>90500</v>
+        <v>78484</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5005,21 +5019,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5029,10 +5043,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537409</v>
+        <v>537387</v>
       </c>
       <c r="R40" t="n">
-        <v>7199912</v>
+        <v>7199785</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5064,7 +5078,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5074,7 +5088,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5101,10 +5115,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118328992</v>
+        <v>118329007</v>
       </c>
       <c r="B41" t="n">
-        <v>90518</v>
+        <v>78484</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5117,21 +5131,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5141,10 +5155,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537379</v>
+        <v>537391</v>
       </c>
       <c r="R41" t="n">
-        <v>7199772</v>
+        <v>7200021</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5176,7 +5190,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5186,7 +5200,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5213,10 +5227,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118329024</v>
+        <v>118328992</v>
       </c>
       <c r="B42" t="n">
-        <v>90522</v>
+        <v>90518</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5229,21 +5243,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5253,10 +5267,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>537525</v>
+        <v>537379</v>
       </c>
       <c r="R42" t="n">
-        <v>7199795</v>
+        <v>7199772</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5288,7 +5302,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5298,7 +5312,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5325,10 +5339,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118329012</v>
+        <v>118329037</v>
       </c>
       <c r="B43" t="n">
-        <v>56494</v>
+        <v>78484</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,48 +5355,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>537396</v>
+        <v>537378</v>
       </c>
       <c r="R43" t="n">
-        <v>7200050</v>
+        <v>7199728</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5451,7 +5451,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118329010</v>
+        <v>118328995</v>
       </c>
       <c r="B44" t="n">
         <v>90522</v>
@@ -5491,10 +5491,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>537411</v>
+        <v>537374</v>
       </c>
       <c r="R44" t="n">
-        <v>7200013</v>
+        <v>7199782</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5563,10 +5563,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118329023</v>
+        <v>118329039</v>
       </c>
       <c r="B45" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5579,34 +5579,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>537496</v>
+        <v>537668</v>
       </c>
       <c r="R45" t="n">
-        <v>7199805</v>
+        <v>7199586</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5638,7 +5643,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5648,7 +5653,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5675,10 +5680,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118329039</v>
+        <v>118329005</v>
       </c>
       <c r="B46" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5691,39 +5696,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>537668</v>
+        <v>537438</v>
       </c>
       <c r="R46" t="n">
-        <v>7199586</v>
+        <v>7199979</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5792,10 +5792,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118329028</v>
+        <v>118329010</v>
       </c>
       <c r="B47" t="n">
-        <v>74596</v>
+        <v>90522</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5808,21 +5808,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5832,10 +5832,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>537517</v>
+        <v>537411</v>
       </c>
       <c r="R47" t="n">
-        <v>7199772</v>
+        <v>7200013</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5867,7 +5867,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,10 +5904,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118329042</v>
+        <v>118329003</v>
       </c>
       <c r="B48" t="n">
-        <v>78484</v>
+        <v>74596</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5920,21 +5920,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>537669</v>
+        <v>537439</v>
       </c>
       <c r="R48" t="n">
-        <v>7199580</v>
+        <v>7199979</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6016,7 +6016,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118328996</v>
+        <v>118329001</v>
       </c>
       <c r="B49" t="n">
         <v>78484</v>
@@ -6056,10 +6056,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>537387</v>
+        <v>537409</v>
       </c>
       <c r="R49" t="n">
-        <v>7199785</v>
+        <v>7199912</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6128,10 +6128,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118329022</v>
+        <v>118328993</v>
       </c>
       <c r="B50" t="n">
-        <v>90522</v>
+        <v>78484</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6144,21 +6144,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6168,10 +6168,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>537492</v>
+        <v>537379</v>
       </c>
       <c r="R50" t="n">
-        <v>7199822</v>
+        <v>7199772</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD50" t="b">

--- a/artfynd/A 22161-2024 artfynd.xlsx
+++ b/artfynd/A 22161-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118329018</v>
+        <v>118329041</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537514</v>
+        <v>537669</v>
       </c>
       <c r="R2" t="n">
-        <v>7200002</v>
+        <v>7199580</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118329028</v>
+        <v>118329011</v>
       </c>
       <c r="B3" t="n">
-        <v>74596</v>
+        <v>78491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537517</v>
+        <v>537396</v>
       </c>
       <c r="R3" t="n">
-        <v>7199772</v>
+        <v>7200015</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118329038</v>
+        <v>118328993</v>
       </c>
       <c r="B4" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>537273</v>
+        <v>537379</v>
       </c>
       <c r="R4" t="n">
-        <v>7199736</v>
+        <v>7199772</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118329012</v>
+        <v>118329040</v>
       </c>
       <c r="B5" t="n">
-        <v>56494</v>
+        <v>78491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,48 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>537396</v>
+        <v>537668</v>
       </c>
       <c r="R5" t="n">
-        <v>7200050</v>
+        <v>7199583</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1105,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118328999</v>
+        <v>118329010</v>
       </c>
       <c r="B6" t="n">
-        <v>78484</v>
+        <v>90529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>537388</v>
+        <v>537411</v>
       </c>
       <c r="R6" t="n">
-        <v>7199825</v>
+        <v>7200013</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1217,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118329016</v>
+        <v>118329037</v>
       </c>
       <c r="B7" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>537389</v>
+        <v>537378</v>
       </c>
       <c r="R7" t="n">
-        <v>7200072</v>
+        <v>7199728</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118329002</v>
+        <v>118328996</v>
       </c>
       <c r="B8" t="n">
-        <v>77421</v>
+        <v>78491</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>537439</v>
+        <v>537387</v>
       </c>
       <c r="R8" t="n">
-        <v>7199979</v>
+        <v>7199785</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118329023</v>
+        <v>118329036</v>
       </c>
       <c r="B9" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>537496</v>
+        <v>537378</v>
       </c>
       <c r="R9" t="n">
-        <v>7199805</v>
+        <v>7199728</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118329014</v>
+        <v>118329012</v>
       </c>
       <c r="B10" t="n">
-        <v>78484</v>
+        <v>56494</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,34 +1597,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537395</v>
+        <v>537396</v>
       </c>
       <c r="R10" t="n">
-        <v>7200052</v>
+        <v>7200050</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1702,10 +1707,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118329026</v>
+        <v>118329042</v>
       </c>
       <c r="B11" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537517</v>
+        <v>537669</v>
       </c>
       <c r="R11" t="n">
-        <v>7199772</v>
+        <v>7199580</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118329042</v>
+        <v>118329020</v>
       </c>
       <c r="B12" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>537669</v>
+        <v>537526</v>
       </c>
       <c r="R12" t="n">
-        <v>7199580</v>
+        <v>7199903</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1889,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118329022</v>
+        <v>118329016</v>
       </c>
       <c r="B13" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1966,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>537492</v>
+        <v>537389</v>
       </c>
       <c r="R13" t="n">
-        <v>7199822</v>
+        <v>7200072</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2043,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118329030</v>
+        <v>118328994</v>
       </c>
       <c r="B14" t="n">
-        <v>90518</v>
+        <v>90476</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,25 +2055,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2078,10 +2083,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>537477</v>
+        <v>537379</v>
       </c>
       <c r="R14" t="n">
-        <v>7199754</v>
+        <v>7199772</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2113,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2123,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2150,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118329041</v>
+        <v>118329027</v>
       </c>
       <c r="B15" t="n">
-        <v>57290</v>
+        <v>77428</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2166,39 +2171,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>537669</v>
+        <v>537517</v>
       </c>
       <c r="R15" t="n">
-        <v>7199580</v>
+        <v>7199772</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2393,10 +2393,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118329020</v>
+        <v>118329044</v>
       </c>
       <c r="B17" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2433,10 +2433,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>537526</v>
+        <v>537667</v>
       </c>
       <c r="R17" t="n">
-        <v>7199903</v>
+        <v>7199573</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118328994</v>
+        <v>118329019</v>
       </c>
       <c r="B18" t="n">
-        <v>90469</v>
+        <v>78573</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2517,25 +2517,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>537379</v>
+        <v>537526</v>
       </c>
       <c r="R18" t="n">
-        <v>7199772</v>
+        <v>7199903</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,10 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118329015</v>
+        <v>118329023</v>
       </c>
       <c r="B19" t="n">
-        <v>90518</v>
+        <v>78491</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2633,21 +2633,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2657,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>537389</v>
+        <v>537496</v>
       </c>
       <c r="R19" t="n">
-        <v>7200072</v>
+        <v>7199805</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118329031</v>
+        <v>118328997</v>
       </c>
       <c r="B20" t="n">
-        <v>96801</v>
+        <v>90529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2741,25 +2741,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>537476</v>
+        <v>537389</v>
       </c>
       <c r="R20" t="n">
-        <v>7199761</v>
+        <v>7199825</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2804,7 +2804,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118329025</v>
+        <v>118329043</v>
       </c>
       <c r="B21" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,34 +2857,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537489</v>
+        <v>537669</v>
       </c>
       <c r="R21" t="n">
-        <v>7199777</v>
+        <v>7199575</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2916,7 +2921,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2926,7 +2931,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,10 +2958,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118329006</v>
+        <v>118329001</v>
       </c>
       <c r="B22" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2969,48 +2974,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537391</v>
+        <v>537409</v>
       </c>
       <c r="R22" t="n">
-        <v>7200021</v>
+        <v>7199912</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3042,7 +3033,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3052,7 +3043,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,10 +3070,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118329046</v>
+        <v>118329005</v>
       </c>
       <c r="B23" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,10 +3110,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537684</v>
+        <v>537438</v>
       </c>
       <c r="R23" t="n">
-        <v>7199558</v>
+        <v>7199979</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3154,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3182,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118329040</v>
+        <v>118329029</v>
       </c>
       <c r="B24" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3231,10 +3222,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>537668</v>
+        <v>537488</v>
       </c>
       <c r="R24" t="n">
-        <v>7199583</v>
+        <v>7199796</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3266,7 +3257,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3267,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,10 +3294,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118329032</v>
+        <v>118329039</v>
       </c>
       <c r="B25" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3319,34 +3310,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>537478</v>
+        <v>537668</v>
       </c>
       <c r="R25" t="n">
-        <v>7199763</v>
+        <v>7199586</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3378,7 +3374,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3384,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3415,10 +3411,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118329000</v>
+        <v>118329030</v>
       </c>
       <c r="B26" t="n">
-        <v>90500</v>
+        <v>90525</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3431,21 +3427,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1108</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,10 +3451,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>537409</v>
+        <v>537477</v>
       </c>
       <c r="R26" t="n">
-        <v>7199912</v>
+        <v>7199754</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3490,7 +3486,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3496,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,10 +3523,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118329045</v>
+        <v>118329028</v>
       </c>
       <c r="B27" t="n">
-        <v>57290</v>
+        <v>74603</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3543,39 +3539,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>537683</v>
+        <v>537517</v>
       </c>
       <c r="R27" t="n">
-        <v>7199559</v>
+        <v>7199772</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3607,7 +3598,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3617,7 +3608,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3644,10 +3635,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118329043</v>
+        <v>118329026</v>
       </c>
       <c r="B28" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3660,39 +3651,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>537669</v>
+        <v>537517</v>
       </c>
       <c r="R28" t="n">
-        <v>7199575</v>
+        <v>7199772</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3724,7 +3710,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3734,7 +3720,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3761,10 +3747,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118329024</v>
+        <v>118328995</v>
       </c>
       <c r="B29" t="n">
-        <v>90522</v>
+        <v>90529</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3801,10 +3787,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>537525</v>
+        <v>537374</v>
       </c>
       <c r="R29" t="n">
-        <v>7199795</v>
+        <v>7199782</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3836,7 +3822,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3846,7 +3832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3873,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118329044</v>
+        <v>118329046</v>
       </c>
       <c r="B30" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3913,10 +3899,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>537667</v>
+        <v>537684</v>
       </c>
       <c r="R30" t="n">
-        <v>7199573</v>
+        <v>7199558</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3948,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3958,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3985,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118329011</v>
+        <v>118328999</v>
       </c>
       <c r="B31" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4025,10 +4011,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>537396</v>
+        <v>537388</v>
       </c>
       <c r="R31" t="n">
-        <v>7200015</v>
+        <v>7199825</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4060,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4070,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4097,10 +4083,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118329029</v>
+        <v>118329000</v>
       </c>
       <c r="B32" t="n">
-        <v>78484</v>
+        <v>90507</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4113,21 +4099,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4137,10 +4123,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>537488</v>
+        <v>537409</v>
       </c>
       <c r="R32" t="n">
-        <v>7199796</v>
+        <v>7199912</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4172,7 +4158,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4182,7 +4168,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4209,10 +4195,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118329009</v>
+        <v>118329006</v>
       </c>
       <c r="B33" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4225,34 +4211,48 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>537409</v>
+        <v>537391</v>
       </c>
       <c r="R33" t="n">
-        <v>7199992</v>
+        <v>7200021</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4321,10 +4321,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118329017</v>
+        <v>118329009</v>
       </c>
       <c r="B34" t="n">
-        <v>74588</v>
+        <v>78491</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4337,21 +4337,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4361,10 +4361,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>537512</v>
+        <v>537409</v>
       </c>
       <c r="R34" t="n">
-        <v>7200008</v>
+        <v>7199992</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4433,10 +4433,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118329036</v>
+        <v>118329007</v>
       </c>
       <c r="B35" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4449,39 +4449,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>537378</v>
+        <v>537391</v>
       </c>
       <c r="R35" t="n">
-        <v>7199728</v>
+        <v>7200021</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4513,7 +4508,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4523,7 +4518,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4550,10 +4545,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118328997</v>
+        <v>118329032</v>
       </c>
       <c r="B36" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4566,21 +4561,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4590,10 +4585,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>537389</v>
+        <v>537478</v>
       </c>
       <c r="R36" t="n">
-        <v>7199825</v>
+        <v>7199763</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4625,7 +4620,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4635,7 +4630,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,10 +4657,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118329008</v>
+        <v>118329022</v>
       </c>
       <c r="B37" t="n">
-        <v>57290</v>
+        <v>90529</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4678,39 +4673,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>537409</v>
+        <v>537492</v>
       </c>
       <c r="R37" t="n">
-        <v>7199992</v>
+        <v>7199822</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4742,7 +4732,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4752,7 +4742,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4779,10 +4769,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118329027</v>
+        <v>118329008</v>
       </c>
       <c r="B38" t="n">
-        <v>77421</v>
+        <v>57290</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4795,34 +4785,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>537517</v>
+        <v>537409</v>
       </c>
       <c r="R38" t="n">
-        <v>7199772</v>
+        <v>7199992</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4854,7 +4849,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4864,7 +4859,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4891,10 +4886,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118329019</v>
+        <v>118329002</v>
       </c>
       <c r="B39" t="n">
-        <v>78566</v>
+        <v>77428</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4907,21 +4902,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>864</v>
+        <v>228579</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4931,10 +4926,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>537526</v>
+        <v>537439</v>
       </c>
       <c r="R39" t="n">
-        <v>7199903</v>
+        <v>7199979</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4966,7 +4961,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4976,7 +4971,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5003,10 +4998,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118328996</v>
+        <v>118329017</v>
       </c>
       <c r="B40" t="n">
-        <v>78484</v>
+        <v>74595</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5019,21 +5014,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5043,10 +5038,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>537387</v>
+        <v>537512</v>
       </c>
       <c r="R40" t="n">
-        <v>7199785</v>
+        <v>7200008</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5078,7 +5073,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5088,7 +5083,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5115,10 +5110,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118329007</v>
+        <v>118329014</v>
       </c>
       <c r="B41" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5155,10 +5150,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>537391</v>
+        <v>537395</v>
       </c>
       <c r="R41" t="n">
-        <v>7200021</v>
+        <v>7200052</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5190,7 +5185,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5200,7 +5195,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5227,10 +5222,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118328992</v>
+        <v>118329034</v>
       </c>
       <c r="B42" t="n">
-        <v>90518</v>
+        <v>57290</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5243,34 +5238,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>537379</v>
+        <v>537458</v>
       </c>
       <c r="R42" t="n">
-        <v>7199772</v>
+        <v>7199716</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5339,10 +5339,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118329037</v>
+        <v>118329031</v>
       </c>
       <c r="B43" t="n">
-        <v>78484</v>
+        <v>96808</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5351,25 +5351,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5379,10 +5379,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>537378</v>
+        <v>537476</v>
       </c>
       <c r="R43" t="n">
-        <v>7199728</v>
+        <v>7199761</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5424,7 +5424,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5451,10 +5451,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118328995</v>
+        <v>118329045</v>
       </c>
       <c r="B44" t="n">
-        <v>90522</v>
+        <v>57290</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5467,34 +5467,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>537374</v>
+        <v>537683</v>
       </c>
       <c r="R44" t="n">
-        <v>7199782</v>
+        <v>7199559</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5526,7 +5531,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5536,7 +5541,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5563,7 +5568,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118329039</v>
+        <v>118329038</v>
       </c>
       <c r="B45" t="n">
         <v>57290</v>
@@ -5608,10 +5613,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>537668</v>
+        <v>537273</v>
       </c>
       <c r="R45" t="n">
-        <v>7199586</v>
+        <v>7199736</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5643,7 +5648,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5653,7 +5658,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5680,10 +5685,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118329005</v>
+        <v>118328992</v>
       </c>
       <c r="B46" t="n">
-        <v>78484</v>
+        <v>90525</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5696,21 +5701,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5720,10 +5725,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>537438</v>
+        <v>537379</v>
       </c>
       <c r="R46" t="n">
-        <v>7199979</v>
+        <v>7199772</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5755,7 +5760,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5765,7 +5770,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5792,10 +5797,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118329010</v>
+        <v>118329025</v>
       </c>
       <c r="B47" t="n">
-        <v>90522</v>
+        <v>78491</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5808,21 +5813,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5832,10 +5837,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>537411</v>
+        <v>537489</v>
       </c>
       <c r="R47" t="n">
-        <v>7200013</v>
+        <v>7199777</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5867,7 +5872,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5877,7 +5882,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5904,10 +5909,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118329003</v>
+        <v>118329024</v>
       </c>
       <c r="B48" t="n">
-        <v>74596</v>
+        <v>90529</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5920,21 +5925,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5944,10 +5949,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>537439</v>
+        <v>537525</v>
       </c>
       <c r="R48" t="n">
-        <v>7199979</v>
+        <v>7199795</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5979,7 +5984,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5989,7 +5994,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6016,10 +6021,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118329001</v>
+        <v>118329018</v>
       </c>
       <c r="B49" t="n">
-        <v>78484</v>
+        <v>78491</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6056,10 +6061,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>537409</v>
+        <v>537514</v>
       </c>
       <c r="R49" t="n">
-        <v>7199912</v>
+        <v>7200002</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6091,7 +6096,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6101,7 +6106,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6128,10 +6133,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118328993</v>
+        <v>118329003</v>
       </c>
       <c r="B50" t="n">
-        <v>78484</v>
+        <v>74603</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6144,21 +6149,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6168,10 +6173,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>537379</v>
+        <v>537439</v>
       </c>
       <c r="R50" t="n">
-        <v>7199772</v>
+        <v>7199979</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6203,7 +6208,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6213,7 +6218,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6240,10 +6245,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118329034</v>
+        <v>118329015</v>
       </c>
       <c r="B51" t="n">
-        <v>57290</v>
+        <v>90525</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6256,39 +6261,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>537458</v>
+        <v>537389</v>
       </c>
       <c r="R51" t="n">
-        <v>7199716</v>
+        <v>7200072</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 22161-2024 artfynd.xlsx
+++ b/artfynd/A 22161-2024 artfynd.xlsx
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118329012</v>
+        <v>118329042</v>
       </c>
       <c r="B10" t="n">
-        <v>56494</v>
+        <v>78491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,48 +1597,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>pulli/nyligen flygga ungar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>537396</v>
+        <v>537669</v>
       </c>
       <c r="R10" t="n">
-        <v>7200050</v>
+        <v>7199580</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1707,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118329042</v>
+        <v>118329012</v>
       </c>
       <c r="B11" t="n">
-        <v>78491</v>
+        <v>56494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,34 +1709,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>537669</v>
+        <v>537396</v>
       </c>
       <c r="R11" t="n">
-        <v>7199580</v>
+        <v>7200050</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2841,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118329043</v>
+        <v>118329001</v>
       </c>
       <c r="B21" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,39 +2857,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>537669</v>
+        <v>537409</v>
       </c>
       <c r="R21" t="n">
-        <v>7199575</v>
+        <v>7199912</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2921,7 +2916,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2931,7 +2926,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2958,7 +2953,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118329001</v>
+        <v>118329005</v>
       </c>
       <c r="B22" t="n">
         <v>78491</v>
@@ -2998,10 +2993,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>537409</v>
+        <v>537438</v>
       </c>
       <c r="R22" t="n">
-        <v>7199912</v>
+        <v>7199979</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3033,7 +3028,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3043,7 +3038,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,10 +3065,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118329005</v>
+        <v>118329043</v>
       </c>
       <c r="B23" t="n">
-        <v>78491</v>
+        <v>57290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3086,34 +3081,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Gäddbäcksberget, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>537438</v>
+        <v>537669</v>
       </c>
       <c r="R23" t="n">
-        <v>7199979</v>
+        <v>7199575</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3145,7 +3145,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 22161-2024 artfynd.xlsx
+++ b/artfynd/A 22161-2024 artfynd.xlsx
@@ -4198,7 +4198,7 @@
         <v>118329006</v>
       </c>
       <c r="B33" t="n">
-        <v>57290</v>
+        <v>57384</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
